--- a/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/项目责任矩阵.xlsx
+++ b/mock数据/JD2项目_test-boq/早期介入/交付预案/输出结果/项目责任矩阵.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
